--- a/тест/test.xlsx
+++ b/тест/test.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сотрудники" sheetId="1" r:id="R22db2962dc5f4d6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сотрудники" sheetId="1" r:id="R1a99809dfaa94f2f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,6 +34,10 @@
     <x:t>02.10.2010</x:t>
   </x:si>
 </x:sst>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/тест/test.xlsx
+++ b/тест/test.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сотрудники" sheetId="1" r:id="R1a99809dfaa94f2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сотрудники" sheetId="1" r:id="Rd5346ed0452b44ce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,17 +27,45 @@
   <x:si>
     <x:t>Фронтенщик</x:t>
   </x:si>
-  <x:si>
-    <x:t>01.01.1999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02.10.2010</x:t>
-  </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts>
+    <x:numFmt numFmtId="14" formatCode="dd.mm.yyyy"/>
+  </x:numFmts>
+  <x:fonts>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:charset val="204"/>
+      <x:scheme val="minor"/>
+    </x:font>
+  </x:fonts>
+  <x:fills>
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+  </x:fills>
+  <x:borders>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0"/>
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  </x:cellXfs>
+</x:styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -71,11 +99,11 @@
       <x:c r="B2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C2" t="s">
-        <x:v>6</x:v>
+      <x:c r="C2" s="1">
+        <x:v>36506</x:v>
       </x:c>
-      <x:c r="D2" t="s">
-        <x:v>7</x:v>
+      <x:c r="D2" s="1">
+        <x:v>46083,42542824074</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/тест/test.xlsx
+++ b/тест/test.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сотрудники" sheetId="1" r:id="Rd5346ed0452b44ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сотрудники" sheetId="1" r:id="R2cc2356487114844"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10,31 +10,14 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>ФИО сотрудника</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Должность сотрудника</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Дата рождения сотрудника</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Дата приема сотрудника на работу</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Иванов Иван Иванович</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Фронтенщик</x:t>
+    <x:t>Hello World!</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts>
-    <x:numFmt numFmtId="14" formatCode="dd.mm.yyyy"/>
-  </x:numFmts>
+  <x:numFmts/>
   <x:fonts>
     <x:font>
       <x:sz val="11"/>
@@ -57,13 +40,27 @@
       <x:bottom/>
       <x:diagonal/>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="fff"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="fff"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="fff"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="fff"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
   <x:cellXfs>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0"/>
-    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </x:cellXfs>
 </x:styleSheet>
 </file>
@@ -71,40 +68,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:dimension ref="A1"/>
-  <x:cols>
-    <x:col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <x:col min="3" max="3" width="28.799999999999997" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="38.4" bestFit="1" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="s">
+      <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" t="s">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="B1" s="1"/>
+      <x:c r="C1" s="1"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="1">
-        <x:v>36506</x:v>
-      </x:c>
-      <x:c r="D2" s="1">
-        <x:v>46083,42542824074</x:v>
-      </x:c>
+      <x:c r="A2" s="1"/>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="1"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
     </x:row>
   </x:sheetData>
 </x:worksheet>

--- a/тест/test.xlsx
+++ b/тест/test.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сотрудники" sheetId="1" r:id="R2cc2356487114844"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Паспорт" sheetId="1" r:id="R1783af91f2134aaa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10,7 +10,139 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>Hello World!</x:t>
+    <x:t>ПАСПОРТ РИСКА - НАКОПЛЕННЫЕ РИСК-СОБЫТИЯ ЗА 2026 ГОД</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Порядковый номер</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Наименование риска</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Триггер (условие фиксации риск-события)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Дата фиксации риск-события</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Описание риск-инцидента</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Оценка значимости (уровень ущерба)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Мероприятия и/или процедуры по управлению риском, минимизация остаточного риска</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Владелец риска</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Перечень источников информации, используемых для идентификации и оценки риска</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Отметка о выполнении мероприятия</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Примечание срок исполнения мероприятий по управлению рисками</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Группа 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Триггер 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Фиксация даты 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Описания 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Оценка 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Событие 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Главный 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Список 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Вып 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>note 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Группа 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Триггер 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Фиксация даты 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Описания 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Оценка 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Событие 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Главный 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Список 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Вып 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>note 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Группа 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Триггер 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Фиксация даты 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Описания 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Оценка 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Событие 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Главный 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Список 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Вып 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>note 2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -25,6 +157,16 @@
       <x:family val="2"/>
       <x:charset val="204"/>
       <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Arial"/>
     </x:font>
   </x:fonts>
   <x:fills>
@@ -41,18 +183,10 @@
       <x:diagonal/>
     </x:border>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="fff"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="fff"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="fff"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="fff"/>
-      </x:bottom>
+      <x:left style="thin"/>
+      <x:right style="thin"/>
+      <x:top style="thin"/>
+      <x:bottom style="thin"/>
     </x:border>
   </x:borders>
   <x:cellStyleXfs>
@@ -60,7 +194,13 @@
   </x:cellStyleXfs>
   <x:cellXfs>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
 </x:styleSheet>
 </file>
@@ -68,24 +208,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:dimension ref="A1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13" customWidth="1"/>
+    <x:col min="2" max="2" width="15" customWidth="1"/>
+    <x:col min="3" max="3" width="23" customWidth="1"/>
+    <x:col min="4" max="4" width="17.5" customWidth="1"/>
+    <x:col min="5" max="5" width="33" customWidth="1"/>
+    <x:col min="6" max="6" width="21" customWidth="1"/>
+    <x:col min="7" max="7" width="55.5" customWidth="1"/>
+    <x:col min="8" max="8" width="28" customWidth="1"/>
+    <x:col min="9" max="9" width="28" customWidth="1"/>
+    <x:col min="10" max="10" width="22.5" customWidth="1"/>
+    <x:col min="11" max="11" width="17" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="1"/>
-      <x:c r="C1" s="1"/>
+      <x:c r="B1"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="1"/>
-      <x:c r="B2" s="1"/>
-      <x:c r="C2" s="1"/>
+      <x:c r="A2" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D2" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E2" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F2" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H2" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I2" s="3" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K2" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="1"/>
-      <x:c r="B3" s="1"/>
-      <x:c r="C3" s="1"/>
+      <x:c r="A3" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K3" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D4" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E4" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F4" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G4" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H4" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I4" s="3" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J4" s="3" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K4" s="3" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D5" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F5" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G5" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H5" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I5" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J5" s="3" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K5" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:K1"/>
+  </x:mergeCells>
 </x:worksheet>
 </file>